--- a/r5-ELGA-MOPED-186-unify-extension-nams/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-186-unify-extension-nams/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-24T08:52:52+00:00</t>
+    <t>2024-10-25T07:50:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -560,10 +560,10 @@
     <t>Anzahl der Tage, für welche kein Kostenbeitrag seitens der Krankenanstalt eingehoben wurde</t>
   </si>
   <si>
-    <t>Account.extension:deckungsBerechtigungsRequestReferenz</t>
-  </si>
-  <si>
-    <t>deckungsBerechtigungsRequestReferenz</t>
+    <t>Account.extension:coverageEligibilityRequestRef</t>
+  </si>
+  <si>
+    <t>coverageEligibilityRequestRef</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-coverageEligibilityRequestRef}
@@ -576,10 +576,10 @@
     <t>Referenz vom Account auf den CoverageEligibilityRequest.</t>
   </si>
   <si>
-    <t>Account.extension:anspruchsReferenz</t>
-  </si>
-  <si>
-    <t>anspruchsReferenz</t>
+    <t>Account.extension:claimRef</t>
+  </si>
+  <si>
+    <t>claimRef</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-claimRef}
@@ -1619,9 +1619,9 @@
   <dimension ref="A1:AL77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="56.43359375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.40234375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.22265625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="38.83203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="28.796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-186-unify-extension-nams/StructureDefinition-MOPEDAccount.xlsx
+++ b/r5-ELGA-MOPED-186-unify-extension-nams/StructureDefinition-MOPEDAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T07:50:17+00:00</t>
+    <t>2024-10-29T09:11:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
